--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536303_LIGAREGULARB_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536303_LIGAREGULARB_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1621,7 +1621,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYÉ</t>
+          <t>O. FUENTES PELUFO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1633,67 +1633,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5836</v>
+        <v>0.248</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5836</v>
+        <v>2.0786</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-1.8306</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5836</v>
+        <v>0.4597</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5836</v>
+        <v>-1.0937</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1.5534</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5836</v>
+        <v>2.7118</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5836</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.6433</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-2.2521</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-1.1622</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-1.0899</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.0548</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.0548</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0.2801</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.414</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.1338</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.9863</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.2192</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.7671</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. FUENTES PELUFO</t>
+          <t>B. SAGNA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.248</v>
+        <v>-0.2563</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0786</v>
+        <v>0.5875</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8306</v>
+        <v>-0.8438</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4597</v>
+        <v>-1.049</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0937</v>
+        <v>-4.0703</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5534</v>
+        <v>3.0213</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7118</v>
+        <v>1.1922</v>
       </c>
       <c r="K16" t="n">
-        <v>0.06850000000000001</v>
+        <v>-1.8462</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6433</v>
+        <v>3.0384</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2521</v>
+        <v>-2.2412</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1622</v>
+        <v>-2.2241</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0899</v>
+        <v>-0.017</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0548</v>
+        <v>1.4384</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.2055</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0548</v>
+        <v>1.6439</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2801</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.414</v>
+        <v>-0.3992</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1338</v>
+        <v>-0.2465</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.9863</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.2192</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7671</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. SAGNA</t>
+          <t>S. THOMAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2563</v>
+        <v>-0.849</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5875</v>
+        <v>-2.7172</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8438</v>
+        <v>1.8683</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.049</v>
+        <v>1.5435</v>
       </c>
       <c r="H17" t="n">
-        <v>-4.0703</v>
+        <v>1.252</v>
       </c>
       <c r="I17" t="n">
-        <v>3.0213</v>
+        <v>0.2915</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1922</v>
+        <v>1.4022</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.8462</v>
+        <v>1.2838</v>
       </c>
       <c r="L17" t="n">
-        <v>3.0384</v>
+        <v>0.1184</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2412</v>
+        <v>0.1413</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.2241</v>
+        <v>-0.0318</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.017</v>
+        <v>0.1731</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4384</v>
+        <v>-2.0548</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2055</v>
+        <v>-3.0822</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6439</v>
+        <v>1.0274</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.0979</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3992</v>
+        <v>-0.3385</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2465</v>
+        <v>0.2406</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.2397</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.6986</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.4589</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. THOMAS</t>
+          <t>J. LAFUENTE VELAZQUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.849</v>
+        <v>-2.7863</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.7172</v>
+        <v>0.1035</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8683</v>
+        <v>-2.8898</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5435</v>
+        <v>0.1983</v>
       </c>
       <c r="H18" t="n">
-        <v>1.252</v>
+        <v>-0.771</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2915</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4022</v>
+        <v>2.9759</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2838</v>
+        <v>1.5951</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1184</v>
+        <v>1.3808</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1413</v>
+        <v>-2.7776</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0318</v>
+        <v>-2.366</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1731</v>
+        <v>-0.4116</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.0548</v>
+        <v>-0.8219</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.0822</v>
+        <v>-2.2603</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0274</v>
+        <v>1.4384</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0979</v>
+        <v>-0.9845</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3385</v>
+        <v>-0.6121</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2406</v>
+        <v>-0.3725</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2397</v>
+        <v>-1.1781</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6986</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.4589</v>
+        <v>-1.1781</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. LAFUENTE VELAZQUEZ</t>
+          <t>B. ALVAREZ TORRES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7863</v>
+        <v>-3.2434</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1035</v>
+        <v>-2.3344</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8898</v>
+        <v>-0.909</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1983</v>
+        <v>-2.1487</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.771</v>
+        <v>-3.2304</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9693000000000001</v>
+        <v>1.0817</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9759</v>
+        <v>-0.4599</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5951</v>
+        <v>-1.4479</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3808</v>
+        <v>0.988</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7776</v>
+        <v>-1.6888</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.366</v>
+        <v>-1.7825</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4116</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.8219</v>
+        <v>-0.2055</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2603</v>
+        <v>-1.2329</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4384</v>
+        <v>1.0274</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9845</v>
+        <v>-0.8892</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6121</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3725</v>
+        <v>-0.2476</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1781</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1781</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. ALVAREZ TORRES</t>
+          <t>M. RAGSDALE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2434</v>
+        <v>-3.2522</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3344</v>
+        <v>0.1343</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.909</v>
+        <v>-3.3865</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1487</v>
+        <v>-0.3509</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.2304</v>
+        <v>-0.3674</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0817</v>
+        <v>0.0165</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4599</v>
+        <v>4.0414</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4479</v>
+        <v>1.7515</v>
       </c>
       <c r="L20" t="n">
-        <v>0.988</v>
+        <v>2.2899</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6888</v>
+        <v>-4.3924</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7825</v>
+        <v>-2.1189</v>
       </c>
       <c r="O20" t="n">
-        <v>0.09370000000000001</v>
+        <v>-2.2735</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2055</v>
+        <v>-0.6163999999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.2329</v>
+        <v>-3.2877</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0274</v>
+        <v>2.6713</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8892</v>
+        <v>-0.867</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="U20" t="n">
         <v>-0.2476</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.4178</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.4178</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. RAGSDALE</t>
+          <t>X. TORRENT BAYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2522</v>
+        <v>-3.9083</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1343</v>
+        <v>-3.2924</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.3865</v>
+        <v>-0.6159</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3509</v>
+        <v>-3.8887</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3674</v>
+        <v>0.4098</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0165</v>
+        <v>-4.2985</v>
       </c>
       <c r="J21" t="n">
-        <v>4.0414</v>
+        <v>-1.8629</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7515</v>
+        <v>0.7781</v>
       </c>
       <c r="L21" t="n">
-        <v>2.2899</v>
+        <v>-2.641</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.3924</v>
+        <v>-2.0258</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.1189</v>
+        <v>-0.3682</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.2735</v>
+        <v>-1.6575</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6163999999999999</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.2877</v>
+        <v>-1.0274</v>
       </c>
       <c r="R21" t="n">
-        <v>2.6713</v>
+        <v>1.6439</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.867</v>
+        <v>-0.636</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.4021</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2476</v>
+        <v>-0.2339</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4178</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4178</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYE</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,152 +2297,69 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4918</v>
+        <v>-15.7703</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.876</v>
+        <v>-2.518600000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6159</v>
+        <v>-13.2515</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.4723</v>
+        <v>-6.6246</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1737</v>
+        <v>-7.3342</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.2985</v>
+        <v>0.7098000000000007</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.4465</v>
+        <v>15.4197</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1945</v>
+        <v>5.6276</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.641</v>
+        <v>9.7921</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0258</v>
+        <v>-22.0444</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3682</v>
+        <v>-12.9617</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.6575</v>
+        <v>-9.0824</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6163999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0274</v>
+        <v>-16.4385</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6439</v>
+        <v>16.4386</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.636</v>
+        <v>-6.0904</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4021</v>
+        <v>-4.0066</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2339</v>
+        <v>-2.0842</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-3.0547</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.5069</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>play_by_play_2536303_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SOL GIRONÈS BISBAL BÀSQUET</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-15.7702</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-2.5186</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-13.2515</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-6.6246</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-7.3341</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.7097999999999995</v>
-      </c>
-      <c r="J24" t="n">
-        <v>15.4197</v>
-      </c>
-      <c r="K24" t="n">
-        <v>5.627599999999999</v>
-      </c>
-      <c r="L24" t="n">
-        <v>9.7921</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-22.0444</v>
-      </c>
-      <c r="N24" t="n">
-        <v>-12.9617</v>
-      </c>
-      <c r="O24" t="n">
-        <v>-9.0824</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>-16.4385</v>
-      </c>
-      <c r="R24" t="n">
-        <v>16.4386</v>
-      </c>
-      <c r="S24" t="n">
-        <v>-6.090400000000001</v>
-      </c>
-      <c r="T24" t="n">
-        <v>-4.0066</v>
-      </c>
-      <c r="U24" t="n">
-        <v>-2.0842</v>
-      </c>
-      <c r="V24" t="n">
-        <v>-3.0547</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.5069</v>
-      </c>
-      <c r="X24" t="n">
         <v>-5.561599999999999</v>
       </c>
-      <c r="Y24" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
